--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-FRM-02_proje_kapi_gate_gozden_gecirme_tutanagi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-FRM-02_proje_kapi_gate_gozden_gecirme_tutanagi.xlsx
@@ -982,7 +982,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Proje Kapı (Gate) Gözden Geçirme Tutanağı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Müşteri kapı adları ve olgunluk kısaltmalarının kaynak planından doğrulanması açıklaştırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ee61fa6873343b4"/>
   <x:tableParts count="1">
@@ -1382,7 +1383,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Proje Kapı (Gate) Gözden Geçirme Tutanağı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Müşteri kapı adları ve olgunluk kısaltmalarının kaynak planından doğrulanması açıklaştırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599dbf7448ab4671"/>
   <x:tableParts count="1">
